--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -10946,6 +10946,154 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10979,7 +11127,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -11062,7 +11210,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -11072,7 +11220,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2342,9 +2333,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2735,9 +2723,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2883,9 +2868,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3771,9 +3753,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4164,9 +4143,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4312,9 +4288,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5052,9 +5025,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5200,9 +5170,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5593,9 +5560,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -5741,9 +5705,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6481,9 +6442,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -6629,9 +6587,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="S39" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7022,9 +6977,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7170,9 +7122,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8058,9 +8007,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -8206,9 +8152,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8354,9 +8297,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8502,9 +8442,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8650,9 +8587,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -8798,9 +8732,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8946,9 +8877,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -9094,9 +9022,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9242,9 +9167,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9390,9 +9312,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9538,9 +9457,6 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -9686,9 +9602,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9834,9 +9747,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -9982,9 +9892,6 @@
       <c r="O61" t="n">
         <v>3</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -10130,9 +10037,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -10278,9 +10182,6 @@
       <c r="O63" t="n">
         <v>2</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -10426,9 +10327,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -10574,9 +10472,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10722,9 +10617,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -10870,9 +10762,6 @@
       <c r="O67" t="n">
         <v>2</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -11018,9 +10907,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -11091,6 +10977,151 @@
       <c r="BC68" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>5</v>
+      </c>
+      <c r="O69" t="n">
+        <v>5</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11158,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -11210,7 +11241,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -11220,7 +11251,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -11272,7 +11303,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -8108,12 +8108,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -8152,76 +8152,87 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8248,17 +8259,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8297,76 +8308,165 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>West Nile Virus Illness</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary West Nile virus surveillance notifications combining confirmed and probable cases across neurologic, non-neurologic and asymptomatic infection classifications.</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN50" t="b">
+        <v>1</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8398,12 +8498,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8428,7 +8528,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -8476,42 +8576,42 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -8543,12 +8643,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8573,7 +8673,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -8621,42 +8721,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8818,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -8863,7 +8963,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -8978,12 +9078,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -9008,12 +9108,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -9056,42 +9156,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9123,12 +9223,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -9153,12 +9253,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -9201,42 +9301,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9268,12 +9368,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9298,7 +9398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -9346,42 +9446,42 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9513,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9443,7 +9543,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -9452,13 +9552,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -9491,42 +9591,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9688,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -9703,12 +9803,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9733,7 +9833,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -9742,13 +9842,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9781,42 +9881,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9948,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9878,7 +9978,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -9887,13 +9987,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -9926,42 +10026,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10023,7 +10123,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -10168,7 +10268,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -10177,13 +10277,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -10313,7 +10413,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -10428,12 +10528,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10458,22 +10558,22 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -10506,42 +10606,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -10573,12 +10673,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10603,12 +10703,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -10651,42 +10751,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10718,12 +10818,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10757,13 +10857,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -10796,42 +10896,42 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10863,12 +10963,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10893,7 +10993,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -10941,42 +11041,42 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11138,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -11047,13 +11147,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -11120,6 +11220,296 @@
         </is>
       </c>
       <c r="BC69" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
+      </c>
+      <c r="O71" t="n">
+        <v>5</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -11241,7 +11631,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -11251,7 +11641,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -11271,7 +11661,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -11515,6 +11515,151 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11548,7 +11693,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -11631,7 +11776,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -11641,7 +11786,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -11660,6 +11660,151 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>7</v>
+      </c>
+      <c r="O73" t="n">
+        <v>7</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11693,7 +11838,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -11776,7 +11921,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -11786,7 +11931,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -11838,7 +11983,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -11805,6 +11805,151 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11838,7 +11983,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11921,7 +12066,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -11931,7 +12076,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -11950,6 +11950,151 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>9</v>
+      </c>
+      <c r="O75" t="n">
+        <v>9</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11983,7 +12128,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12211,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -12076,7 +12221,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -12128,7 +12273,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -9513,12 +9513,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9591,42 +9591,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -9658,12 +9658,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -9736,42 +9736,42 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9803,12 +9803,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9842,13 +9842,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9881,42 +9881,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9948,12 +9948,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -9987,13 +9987,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -10026,42 +10026,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -10316,42 +10316,42 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -10422,13 +10422,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -10461,42 +10461,42 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -10528,12 +10528,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10567,13 +10567,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -10606,42 +10606,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10673,12 +10673,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -10712,13 +10712,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -10751,42 +10751,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -10818,12 +10818,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -10896,42 +10896,42 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -11041,42 +11041,42 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11108,12 +11108,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -11147,13 +11147,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -11186,42 +11186,42 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -11253,12 +11253,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -11292,13 +11292,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -11331,42 +11331,42 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11398,12 +11398,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -11437,13 +11437,13 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>0.001432519066384693</v>
+        <v>0</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -11476,42 +11476,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -11582,13 +11582,13 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -11621,42 +11621,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11688,12 +11688,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -11727,13 +11727,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>0.00200552669293857</v>
+        <v>0</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -11766,42 +11766,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11833,12 +11833,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -11872,13 +11872,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -11911,42 +11911,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -11978,12 +11978,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -12017,13 +12017,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0.002578534319492447</v>
+        <v>0</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -12056,40 +12056,185 @@
       </c>
       <c r="AV75" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>9</v>
+      </c>
+      <c r="O76" t="n">
+        <v>9</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW75" t="inlineStr">
+      <c r="AW76" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
+      <c r="AX76" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr">
+      <c r="AY76" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
+      <c r="AZ76" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA75" t="inlineStr">
+      <c r="BA76" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB75" t="inlineStr">
+      <c r="BB76" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC75" t="inlineStr">
+      <c r="BC76" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -12211,7 +12356,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -12221,7 +12366,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d128/2026-2029.xlsx
+++ b/diseases/d128/2026-2029.xlsx
@@ -8108,12 +8108,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -8157,57 +8157,43 @@
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -8217,17 +8203,17 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -8259,17 +8245,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8308,140 +8294,48 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>West Nile Virus Illness</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>PHO IDTO current-year monthly preliminary West Nile virus surveillance notifications combining confirmed and probable cases across neurologic, non-neurologic and asymptomatic infection classifications.</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP50" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ50" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV50" t="inlineStr">
-        <is>
-          <t>pho_idto_monthly</t>
-        </is>
-      </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -8451,17 +8345,17 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -8498,12 +8392,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8542,12 +8436,9 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8576,42 +8467,42 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8643,12 +8534,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8687,12 +8578,9 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8721,42 +8609,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8788,12 +8676,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8818,7 +8706,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -8832,12 +8720,9 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8866,42 +8751,42 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8818,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8963,7 +8848,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -8977,12 +8862,9 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -9011,42 +8893,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9078,12 +8960,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -9108,7 +8990,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -9122,12 +9004,9 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -9156,42 +9035,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9223,12 +9102,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -9253,7 +9132,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -9267,76 +9146,87 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -9363,17 +9253,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9398,12 +9288,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9412,51 +9302,140 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>West Nile Virus Illness</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary West Nile virus surveillance notifications combining confirmed and probable cases across neurologic, non-neurologic and asymptomatic infection classifications.</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN57" t="b">
+        <v>1</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_WEST_NILE_VIRUS_ILLNESS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -9466,17 +9445,17 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -9543,12 +9522,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -9688,12 +9667,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9833,12 +9812,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9948,12 +9927,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9978,22 +9957,22 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -10026,42 +10005,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10102,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -10268,12 +10247,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -10383,12 +10362,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -10413,7 +10392,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -10422,13 +10401,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -10461,42 +10440,42 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10528,12 +10507,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10558,7 +10537,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -10572,12 +10551,9 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10606,42 +10582,42 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10673,12 +10649,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10703,7 +10679,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -10712,17 +10688,14 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>2</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10751,42 +10724,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10818,12 +10791,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -10848,7 +10821,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -10862,12 +10835,9 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10896,42 +10866,42 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10963,12 +10933,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -10993,12 +10963,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -11007,12 +10977,9 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -11046,12 +11013,12 @@
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -11066,12 +11033,12 @@
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
@@ -11108,12 +11075,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -11138,12 +11105,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -11152,12 +11119,9 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -11186,42 +11150,42 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11253,12 +11217,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -11283,26 +11247,23 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>2</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -11331,42 +11292,42 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11398,12 +11359,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -11428,12 +11389,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11442,12 +11403,9 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11476,42 +11434,42 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11501,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11573,26 +11531,23 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>5</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0.001432519066384693</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11621,42 +11576,42 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11688,12 +11643,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11718,12 +11673,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -11766,42 +11721,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11833,12 +11788,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -11863,22 +11818,22 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>0.00200552669293857</v>
+        <v>0</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -11911,42 +11866,42 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12008,12 +11963,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -12153,22 +12108,22 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -12237,6 +12192,3897 @@
       <c r="BC76" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>3</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>2</v>
+      </c>
+      <c r="O81" t="n">
+        <v>2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>2</v>
+      </c>
+      <c r="O93" t="n">
+        <v>2</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>5</v>
+      </c>
+      <c r="O95" t="n">
+        <v>5</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>7</v>
+      </c>
+      <c r="O97" t="n">
+        <v>7</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>9</v>
+      </c>
+      <c r="O99" t="n">
+        <v>9</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>6</v>
+      </c>
+      <c r="O101" t="n">
+        <v>6</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.001719022879661631</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12273,7 +16119,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -12356,7 +16202,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
@@ -12366,7 +16212,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -12418,7 +16264,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
